--- a/data/trans_dic/P1002-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,04; 5,58</t>
+          <t>2,15; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,26; 6,5</t>
+          <t>2,11; 6,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,38</t>
+          <t>2,08; 6,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,04</t>
+          <t>3,05; 7,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,63; 8,83</t>
+          <t>3,9; 9,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,33</t>
+          <t>4,37; 10,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 8,8</t>
+          <t>3,6; 8,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,22; 9,55</t>
+          <t>4,98; 9,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,15</t>
+          <t>3,16; 6,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 7,37</t>
+          <t>3,62; 7,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,35</t>
+          <t>3,37; 6,55</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 7,54</t>
+          <t>4,39; 7,34</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,16</t>
+          <t>2,03; 6,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,84</t>
+          <t>3,22; 8,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,49</t>
+          <t>2,3; 6,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,63</t>
+          <t>1,36; 4,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,11</t>
+          <t>4,65; 9,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,31; 13,53</t>
+          <t>6,49; 13,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,12</t>
+          <t>3,15; 8,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,96</t>
+          <t>5,57; 10,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,22</t>
+          <t>3,83; 7,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 9,1</t>
+          <t>5,29; 9,14</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,32</t>
+          <t>3,2; 6,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,7</t>
+          <t>3,74; 6,74</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 7,34</t>
+          <t>3,54; 7,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,4</t>
+          <t>6,06; 11,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 8,7</t>
+          <t>4,19; 8,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 9,31</t>
+          <t>1,86; 9,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 15,55</t>
+          <t>6,09; 16,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,49; 22,1</t>
+          <t>12,68; 22,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 20,64</t>
+          <t>9,13; 21,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 13,41</t>
+          <t>6,43; 13,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,4</t>
+          <t>4,63; 8,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 13,47</t>
+          <t>8,91; 13,36</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 10,4</t>
+          <t>6,05; 10,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 9,51</t>
+          <t>2,6; 9,52</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,11</t>
+          <t>5,34; 8,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,83; 10,18</t>
+          <t>6,77; 10,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 6,91</t>
+          <t>4,12; 6,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,93</t>
+          <t>4,94; 7,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 10,76</t>
+          <t>6,6; 10,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,66; 14,6</t>
+          <t>9,6; 14,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 12,44</t>
+          <t>8,19; 12,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,45; 8,45</t>
+          <t>3,25; 8,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,29; 8,59</t>
+          <t>6,22; 8,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,39; 11,29</t>
+          <t>8,38; 11,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 8,58</t>
+          <t>6,27; 8,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,5</t>
+          <t>4,46; 7,42</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,89</t>
+          <t>3,43; 8,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,3</t>
+          <t>3,98; 8,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,35; 9,43</t>
+          <t>5,54; 9,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,37</t>
+          <t>5,7; 10,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,64</t>
+          <t>6,64; 11,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,26; 22,06</t>
+          <t>16,11; 22,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,49</t>
+          <t>12,31; 17,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,03; 15,25</t>
+          <t>9,49; 15,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,07; 9,82</t>
+          <t>6,12; 9,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,79</t>
+          <t>11,92; 15,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,72; 13,37</t>
+          <t>9,76; 13,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 12,89</t>
+          <t>8,89; 12,78</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,89</t>
+          <t>1,62; 6,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,5</t>
+          <t>2,24; 7,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,79</t>
+          <t>1,9; 6,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 10,52</t>
+          <t>1,97; 10,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,51; 10,93</t>
+          <t>7,31; 10,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,62; 16,81</t>
+          <t>12,61; 16,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,35</t>
+          <t>9,32; 13,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,03; 16,27</t>
+          <t>11,98; 16,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,54</t>
+          <t>6,52; 9,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,97; 14,67</t>
+          <t>10,83; 14,37</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 11,38</t>
+          <t>8,07; 11,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,98; 13,74</t>
+          <t>9,85; 13,79</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,04</t>
+          <t>4,46; 6,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 7,55</t>
+          <t>5,8; 7,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,2</t>
+          <t>4,63; 6,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,42</t>
+          <t>4,11; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,5; 9,48</t>
+          <t>7,6; 9,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,72; 15,14</t>
+          <t>12,85; 15,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,63; 11,86</t>
+          <t>9,73; 11,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,97; 11,03</t>
+          <t>8,18; 10,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,29; 7,49</t>
+          <t>6,3; 7,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 11,12</t>
+          <t>9,65; 11,14</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,42; 8,74</t>
+          <t>7,41; 8,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,54</t>
+          <t>6,64; 8,53</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9674; 26415</t>
+          <t>10176; 26309</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9860; 28344</t>
+          <t>9212; 27154</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9520; 27395</t>
+          <t>8910; 26956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16075; 35567</t>
+          <t>15423; 36076</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11136; 27085</t>
+          <t>11955; 28360</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14011; 32487</t>
+          <t>13754; 33594</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12749; 30533</t>
+          <t>12481; 30206</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23348; 42741</t>
+          <t>22286; 42173</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24966; 47971</t>
+          <t>24672; 48840</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27719; 55338</t>
+          <t>27187; 53466</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26589; 49300</t>
+          <t>26142; 50808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44549; 71842</t>
+          <t>41862; 69945</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7406; 22606</t>
+          <t>7437; 23263</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12695; 32824</t>
+          <t>13465; 35353</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8558; 24491</t>
+          <t>8690; 24339</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6138; 20960</t>
+          <t>6152; 19432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16915; 37582</t>
+          <t>17276; 36852</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21322; 45726</t>
+          <t>21942; 46156</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11083; 30238</t>
+          <t>11719; 30863</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22735; 41945</t>
+          <t>21311; 41921</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28285; 53311</t>
+          <t>28276; 52088</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38086; 68901</t>
+          <t>40034; 69162</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23553; 47336</t>
+          <t>23992; 50576</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31636; 55959</t>
+          <t>31216; 56285</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18576; 39819</t>
+          <t>19188; 39890</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38917; 71740</t>
+          <t>38123; 69996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22098; 45390</t>
+          <t>21869; 44122</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11796; 62190</t>
+          <t>12460; 64029</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9570; 26096</t>
+          <t>10220; 27199</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32492; 57477</t>
+          <t>32977; 58048</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14920; 34293</t>
+          <t>15162; 36244</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>11068; 22377</t>
+          <t>10734; 22029</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32864; 59687</t>
+          <t>32849; 58641</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>80269; 119780</t>
+          <t>79247; 118861</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42445; 71527</t>
+          <t>41659; 71566</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21026; 79403</t>
+          <t>21714; 79493</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66240; 100450</t>
+          <t>66130; 100191</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79104; 117996</t>
+          <t>78499; 118536</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48144; 79407</t>
+          <t>47421; 79113</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51693; 82007</t>
+          <t>51043; 80929</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47702; 76887</t>
+          <t>47172; 77775</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74050; 111949</t>
+          <t>73618; 109061</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66998; 102723</t>
+          <t>67661; 101395</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33747; 82657</t>
+          <t>31765; 83697</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122846; 167770</t>
+          <t>121390; 167084</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>161593; 217410</t>
+          <t>161303; 215704</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>122217; 169548</t>
+          <t>123866; 167204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89780; 150760</t>
+          <t>89629; 149285</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12362; 31161</t>
+          <t>12035; 30615</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19892; 42294</t>
+          <t>20276; 42090</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33215; 58560</t>
+          <t>34396; 60955</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27053; 49244</t>
+          <t>27075; 48944</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>38247; 66182</t>
+          <t>37751; 65716</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>123522; 167569</t>
+          <t>122322; 167724</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>89911; 129136</t>
+          <t>90847; 132097</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>75952; 128201</t>
+          <t>79818; 129764</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>55806; 90311</t>
+          <t>56263; 89708</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>147732; 200362</t>
+          <t>151319; 201429</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132036; 181659</t>
+          <t>132643; 182469</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>115943; 169594</t>
+          <t>116914; 168211</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4884; 17557</t>
+          <t>4838; 18054</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6390; 20014</t>
+          <t>5991; 20727</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5427; 19511</t>
+          <t>5455; 19104</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4332; 25307</t>
+          <t>4740; 24765</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>93833; 136458</t>
+          <t>91316; 132418</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>139984; 186530</t>
+          <t>139927; 185924</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>100792; 144475</t>
+          <t>100835; 145391</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91514; 123731</t>
+          <t>91092; 124231</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>102602; 147600</t>
+          <t>100801; 143491</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>151017; 201848</t>
+          <t>149032; 197740</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110976; 155869</t>
+          <t>110454; 155658</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>99869; 137566</t>
+          <t>98567; 137980</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>145613; 197516</t>
+          <t>145695; 196437</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>197507; 258101</t>
+          <t>198273; 262471</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156069; 210043</t>
+          <t>156808; 212982</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>144413; 216788</t>
+          <t>138822; 213214</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>253226; 320299</t>
+          <t>256750; 320399</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>451249; 537140</t>
+          <t>456096; 541365</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>339962; 418676</t>
+          <t>343723; 419177</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>284887; 394394</t>
+          <t>292594; 392823</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>418258; 498124</t>
+          <t>418523; 496873</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>672406; 774556</t>
+          <t>672140; 776028</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>512978; 604709</t>
+          <t>512483; 612765</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>461284; 593362</t>
+          <t>461699; 592714</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1002-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1002-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,55</t>
+          <t>2,13; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,22</t>
+          <t>2,26; 6,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,28</t>
+          <t>2,01; 6,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,14</t>
+          <t>3,03; 6,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 9,25</t>
+          <t>3,73; 9,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,37; 10,68</t>
+          <t>4,56; 10,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,6; 8,7</t>
+          <t>3,73; 8,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,42</t>
+          <t>5,22; 9,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,26</t>
+          <t>3,17; 6,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 7,12</t>
+          <t>3,65; 7,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,55</t>
+          <t>3,3; 6,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,34</t>
+          <t>4,4; 7,26</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,34</t>
+          <t>1,84; 6,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,44</t>
+          <t>2,97; 7,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,45</t>
+          <t>2,41; 6,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 4,3</t>
+          <t>1,51; 4,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 9,91</t>
+          <t>4,66; 10,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,49; 13,66</t>
+          <t>6,52; 13,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 8,29</t>
+          <t>3,06; 8,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 10,96</t>
+          <t>6,3; 11,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,05</t>
+          <t>3,81; 7,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,29; 9,14</t>
+          <t>5,3; 9,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,75</t>
+          <t>3,25; 6,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,74</t>
+          <t>4,01; 6,87</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,35</t>
+          <t>3,47; 7,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 11,12</t>
+          <t>5,98; 10,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,45</t>
+          <t>4,14; 8,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 9,58</t>
+          <t>5,39; 10,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,09; 16,21</t>
+          <t>5,87; 15,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,68; 22,32</t>
+          <t>12,41; 22,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 21,82</t>
+          <t>9,05; 21,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,2</t>
+          <t>6,33; 13,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,26</t>
+          <t>4,69; 8,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,91; 13,36</t>
+          <t>8,79; 13,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 10,4</t>
+          <t>5,94; 10,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,6; 9,52</t>
+          <t>6,51; 10,65</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>7,04%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 8,09</t>
+          <t>5,25; 8,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,77; 10,23</t>
+          <t>6,76; 10,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,88</t>
+          <t>4,22; 6,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,83</t>
+          <t>5,04; 7,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,6; 10,89</t>
+          <t>6,68; 10,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,6; 14,23</t>
+          <t>9,54; 14,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 12,28</t>
+          <t>8,09; 12,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,56</t>
+          <t>6,65; 9,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 8,56</t>
+          <t>6,13; 8,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,38; 11,2</t>
+          <t>8,35; 11,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,27; 8,46</t>
+          <t>6,29; 8,54</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 7,42</t>
+          <t>6,02; 8,09</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 8,73</t>
+          <t>3,66; 9,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,26</t>
+          <t>3,97; 8,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 9,82</t>
+          <t>5,55; 9,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 10,3</t>
+          <t>5,05; 9,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,64; 11,55</t>
+          <t>6,91; 11,51</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 22,08</t>
+          <t>16,36; 22,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,31; 17,89</t>
+          <t>12,01; 17,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,43</t>
+          <t>11,88; 15,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 9,76</t>
+          <t>5,98; 9,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,92; 15,87</t>
+          <t>11,99; 15,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9,76; 13,43</t>
+          <t>9,66; 13,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,78</t>
+          <t>9,53; 12,37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,05</t>
+          <t>1,56; 5,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 7,77</t>
+          <t>2,42; 7,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,65</t>
+          <t>1,88; 6,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,97; 10,3</t>
+          <t>2,26; 11,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,31; 10,6</t>
+          <t>7,36; 10,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,61; 16,76</t>
+          <t>12,68; 16,86</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,44</t>
+          <t>9,43; 13,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,34</t>
+          <t>11,78; 15,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,52; 9,28</t>
+          <t>6,58; 9,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,83; 14,37</t>
+          <t>10,77; 14,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,07; 11,37</t>
+          <t>8,09; 11,3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 13,79</t>
+          <t>10,0; 13,87</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,01</t>
+          <t>4,45; 6,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,67</t>
+          <t>5,78; 7,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4,63; 6,29</t>
+          <t>4,62; 6,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,11; 6,32</t>
+          <t>5,07; 6,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,6; 9,48</t>
+          <t>7,44; 9,44</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,85; 15,26</t>
+          <t>12,84; 15,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 11,87</t>
+          <t>9,69; 11,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,18; 10,99</t>
+          <t>9,66; 11,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,47</t>
+          <t>6,27; 7,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,65; 11,14</t>
+          <t>9,63; 11,16</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7,41; 8,86</t>
+          <t>7,45; 8,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,64; 8,53</t>
+          <t>7,64; 8,88</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24028</t>
+          <t>25050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31411</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55440</t>
+          <t>59943</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10176; 26309</t>
+          <t>10110; 26970</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9212; 27154</t>
+          <t>9859; 28139</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8910; 26956</t>
+          <t>8646; 27019</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15423; 36076</t>
+          <t>16690; 37955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>11955; 28360</t>
+          <t>11439; 28084</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13754; 33594</t>
+          <t>14350; 33628</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12481; 30206</t>
+          <t>12947; 31196</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22286; 42173</t>
+          <t>25512; 46588</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24672; 48840</t>
+          <t>24703; 47774</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27187; 53466</t>
+          <t>27413; 53848</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26142; 50808</t>
+          <t>25594; 49878</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>41862; 69945</t>
+          <t>45667; 75449</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>42038</t>
+          <t>48106</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7437; 23263</t>
+          <t>6770; 23091</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13465; 35353</t>
+          <t>12448; 31409</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8690; 24339</t>
+          <t>9095; 24998</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6152; 19432</t>
+          <t>7311; 22218</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17276; 36852</t>
+          <t>17335; 37848</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21942; 46156</t>
+          <t>22028; 44657</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11719; 30863</t>
+          <t>11386; 30877</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21311; 41921</t>
+          <t>26653; 48210</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28276; 52088</t>
+          <t>28134; 55043</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40034; 69162</t>
+          <t>40088; 72356</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23992; 50576</t>
+          <t>24376; 51444</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31216; 56285</t>
+          <t>36343; 62279</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15706</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>51926</t>
+          <t>55081</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>19188; 39890</t>
+          <t>18809; 38863</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>38123; 69996</t>
+          <t>37658; 68129</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21869; 44122</t>
+          <t>21617; 44149</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12460; 64029</t>
+          <t>25406; 51583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10220; 27199</t>
+          <t>9854; 26710</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32977; 58048</t>
+          <t>32291; 57783</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15162; 36244</t>
+          <t>15031; 35758</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10734; 22029</t>
+          <t>11870; 25772</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32849; 58641</t>
+          <t>33317; 60801</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79247; 118861</t>
+          <t>78203; 118481</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41659; 71566</t>
+          <t>40899; 72368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21714; 79493</t>
+          <t>42897; 70183</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64566</t>
+          <t>71172</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>61440</t>
+          <t>69063</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>126007</t>
+          <t>140234</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66130; 100191</t>
+          <t>65032; 99225</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78499; 118536</t>
+          <t>78367; 116707</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>47421; 79113</t>
+          <t>48479; 79657</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51043; 80929</t>
+          <t>57023; 87911</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47172; 77775</t>
+          <t>47717; 77526</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73618; 109061</t>
+          <t>73112; 109888</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>67661; 101395</t>
+          <t>66847; 101729</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>31765; 83697</t>
+          <t>57266; 84684</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>121390; 167084</t>
+          <t>119615; 167097</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>161303; 215704</t>
+          <t>160727; 216073</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>123866; 167204</t>
+          <t>124165; 168754</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>89629; 149285</t>
+          <t>119981; 161034</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36377</t>
+          <t>38945</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>106930</t>
+          <t>113418</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>143306</t>
+          <t>152363</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>12035; 30615</t>
+          <t>12842; 31608</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20276; 42090</t>
+          <t>20226; 43158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34396; 60955</t>
+          <t>34440; 59665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27075; 48944</t>
+          <t>28701; 52490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>37751; 65716</t>
+          <t>39281; 65475</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>122322; 167724</t>
+          <t>124277; 168708</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90847; 132097</t>
+          <t>88629; 129508</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>79818; 129764</t>
+          <t>98654; 132527</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>56263; 89708</t>
+          <t>54951; 90103</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151319; 201429</t>
+          <t>152198; 201227</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>132643; 182469</t>
+          <t>131234; 177351</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>116914; 168211</t>
+          <t>133187; 172938</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>106088</t>
+          <t>114845</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>117073</t>
+          <t>127538</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4838; 18054</t>
+          <t>4652; 17355</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5991; 20727</t>
+          <t>6454; 19452</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5455; 19104</t>
+          <t>5399; 19482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4740; 24765</t>
+          <t>5359; 26593</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>91316; 132418</t>
+          <t>91888; 132095</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>139927; 185924</t>
+          <t>140672; 187078</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>100835; 145391</t>
+          <t>101990; 144824</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>91092; 124231</t>
+          <t>99352; 132836</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100801; 143491</t>
+          <t>101815; 145183</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>149032; 197740</t>
+          <t>148287; 197379</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>110454; 155658</t>
+          <t>110769; 154775</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>98567; 137980</t>
+          <t>108063; 149859</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>183351</t>
+          <t>197789</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>352438</t>
+          <t>385477</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>535790</t>
+          <t>583266</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>145695; 196437</t>
+          <t>145474; 196815</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>198273; 262471</t>
+          <t>197558; 262122</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>156808; 212982</t>
+          <t>156497; 208825</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>138822; 213214</t>
+          <t>174348; 229249</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>256750; 320399</t>
+          <t>251166; 318978</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>456096; 541365</t>
+          <t>455599; 540121</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>343723; 419177</t>
+          <t>342123; 417759</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>292594; 392823</t>
+          <t>351064; 420034</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>418523; 496873</t>
+          <t>416556; 505144</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>672140; 776028</t>
+          <t>671339; 777394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>512483; 612765</t>
+          <t>515149; 613574</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>461699; 592714</t>
+          <t>540501; 628193</t>
         </is>
       </c>
     </row>
